--- a/docs/exports/verity_esg_scores.xlsx
+++ b/docs/exports/verity_esg_scores.xlsx
@@ -1272,7 +1272,7 @@
         <v>0.355</v>
       </c>
       <c r="R8" t="n">
-        <v>3.92</v>
+        <v>3.27</v>
       </c>
       <c r="S8" t="n">
         <v>37994</v>
@@ -1352,7 +1352,7 @@
         <v>0.261</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>3.12</v>
+        <v>2.39</v>
       </c>
       <c r="S9" s="4" t="n">
         <v>32534</v>
@@ -1432,7 +1432,7 @@
         <v>0.544</v>
       </c>
       <c r="R10" t="n">
-        <v>5.04</v>
+        <v>4.51</v>
       </c>
       <c r="S10" t="n">
         <v>40411</v>
@@ -1512,7 +1512,7 @@
         <v>1.392</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>8.4</v>
+        <v>8.23</v>
       </c>
       <c r="S11" s="4" t="n">
         <v>49581</v>
@@ -1592,7 +1592,7 @@
         <v>1.007</v>
       </c>
       <c r="R12" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="S12" t="n">
         <v>55106</v>
@@ -1672,7 +1672,7 @@
         <v>0.947</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>7.04</v>
+        <v>6.73</v>
       </c>
       <c r="S13" s="4" t="n">
         <v>68113</v>
@@ -3552,7 +3552,7 @@
         <v>0.822</v>
       </c>
       <c r="R38" t="n">
-        <v>6.24</v>
+        <v>5.84</v>
       </c>
       <c r="S38" t="n">
         <v>38328</v>
@@ -3632,7 +3632,7 @@
         <v>0.423</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>4.32</v>
+        <v>3.72</v>
       </c>
       <c r="S39" s="4" t="n">
         <v>38979</v>
@@ -3712,7 +3712,7 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="R40" t="n">
-        <v>5.2</v>
+        <v>4.69</v>
       </c>
       <c r="S40" t="n">
         <v>39763</v>
@@ -3792,7 +3792,7 @@
         <v>0.605</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>5.36</v>
+        <v>4.87</v>
       </c>
       <c r="S41" s="4" t="n">
         <v>49610</v>
@@ -3872,7 +3872,7 @@
         <v>1.317</v>
       </c>
       <c r="R42" t="n">
-        <v>8</v>
+        <v>7.79</v>
       </c>
       <c r="S42" t="n">
         <v>59205</v>
@@ -3952,7 +3952,7 @@
         <v>1.785</v>
       </c>
       <c r="R43" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S43" s="4" t="n">
         <v>64996</v>
@@ -4482,7 +4482,7 @@
         <v>0.121</v>
       </c>
       <c r="R50" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="S50" t="n">
         <v>12428</v>
@@ -4562,7 +4562,7 @@
         <v>0.144</v>
       </c>
       <c r="R51" s="4" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="S51" s="4" t="n">
         <v>20905</v>
@@ -4642,7 +4642,7 @@
         <v>0.114</v>
       </c>
       <c r="R52" t="n">
-        <v>1.92</v>
+        <v>1.06</v>
       </c>
       <c r="S52" t="n">
         <v>26361</v>
@@ -4722,7 +4722,7 @@
         <v>0.785</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>5.84</v>
+        <v>5.4</v>
       </c>
       <c r="S53" s="4" t="n">
         <v>26754</v>
@@ -4802,7 +4802,7 @@
         <v>1.252</v>
       </c>
       <c r="R54" t="n">
-        <v>7.92</v>
+        <v>7.7</v>
       </c>
       <c r="S54" t="n">
         <v>34340</v>
@@ -4882,7 +4882,7 @@
         <v>1.373</v>
       </c>
       <c r="R55" s="4" t="n">
-        <v>8.24</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="S55" s="4" t="n">
         <v>44780</v>
@@ -6762,7 +6762,7 @@
         <v>0.342</v>
       </c>
       <c r="R80" t="n">
-        <v>3.68</v>
+        <v>3.01</v>
       </c>
       <c r="S80" t="n">
         <v>21948</v>
@@ -6842,7 +6842,7 @@
         <v>0.135</v>
       </c>
       <c r="R81" s="4" t="n">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="S81" s="4" t="n">
         <v>22209</v>
@@ -6922,7 +6922,7 @@
         <v>0.246</v>
       </c>
       <c r="R82" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="S82" t="n">
         <v>18284</v>
@@ -7002,7 +7002,7 @@
         <v>0.065</v>
       </c>
       <c r="R83" s="4" t="n">
-        <v>1.76</v>
+        <v>0.89</v>
       </c>
       <c r="S83" s="4" t="n">
         <v>22987</v>
@@ -7082,7 +7082,7 @@
         <v>0.8</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>5.58</v>
       </c>
       <c r="S84" t="n">
         <v>5627</v>
@@ -7162,7 +7162,7 @@
         <v>0.929</v>
       </c>
       <c r="R85" s="4" t="n">
-        <v>6.88</v>
+        <v>6.55</v>
       </c>
       <c r="S85" s="4" t="n">
         <v>24215</v>
@@ -7242,7 +7242,7 @@
         <v>0.35</v>
       </c>
       <c r="R86" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="S86" t="n">
         <v>25722</v>
@@ -7322,7 +7322,7 @@
         <v>0.341</v>
       </c>
       <c r="R87" s="4" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="S87" s="4" t="n">
         <v>22025</v>
@@ -7402,7 +7402,7 @@
         <v>0.386</v>
       </c>
       <c r="R88" t="n">
-        <v>4.08</v>
+        <v>3.45</v>
       </c>
       <c r="S88" t="n">
         <v>23319</v>
@@ -7482,7 +7482,7 @@
         <v>0.516</v>
       </c>
       <c r="R89" s="4" t="n">
-        <v>4.96</v>
+        <v>4.42</v>
       </c>
       <c r="S89" s="4" t="n">
         <v>20352</v>
@@ -7562,7 +7562,7 @@
         <v>0.171</v>
       </c>
       <c r="R90" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="S90" t="n">
         <v>26387</v>
@@ -7642,7 +7642,7 @@
         <v>0.269</v>
       </c>
       <c r="R91" s="4" t="n">
-        <v>3.2</v>
+        <v>2.48</v>
       </c>
       <c r="S91" s="4" t="n">
         <v>22322</v>
@@ -7722,7 +7722,7 @@
         <v>1.589</v>
       </c>
       <c r="R92" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="S92" t="n">
         <v>37751</v>
@@ -7802,7 +7802,7 @@
         <v>1.406</v>
       </c>
       <c r="R93" s="4" t="n">
-        <v>8.56</v>
+        <v>8.41</v>
       </c>
       <c r="S93" s="4" t="n">
         <v>38410</v>
@@ -7882,7 +7882,7 @@
         <v>1.341</v>
       </c>
       <c r="R94" t="n">
-        <v>8.08</v>
+        <v>7.88</v>
       </c>
       <c r="S94" t="n">
         <v>38021</v>
@@ -7962,7 +7962,7 @@
         <v>1.607</v>
       </c>
       <c r="R95" s="4" t="n">
-        <v>8.960000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="S95" s="4" t="n">
         <v>41073</v>
@@ -8042,7 +8042,7 @@
         <v>1.698</v>
       </c>
       <c r="R96" t="n">
-        <v>9.119999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="S96" t="n">
         <v>39763</v>
@@ -8122,7 +8122,7 @@
         <v>1.789</v>
       </c>
       <c r="R97" s="4" t="n">
-        <v>9.44</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="S97" s="4" t="n">
         <v>40246</v>
@@ -8652,7 +8652,7 @@
         <v>0.546</v>
       </c>
       <c r="R104" t="n">
-        <v>5.12</v>
+        <v>4.6</v>
       </c>
       <c r="S104" t="n">
         <v>16484</v>
@@ -8732,7 +8732,7 @@
         <v>0.335</v>
       </c>
       <c r="R105" s="4" t="n">
-        <v>3.44</v>
+        <v>2.74</v>
       </c>
       <c r="S105" s="4" t="n">
         <v>17935</v>
@@ -8812,7 +8812,7 @@
         <v>0.486</v>
       </c>
       <c r="R106" t="n">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="S106" t="n">
         <v>18537</v>
@@ -8892,7 +8892,7 @@
         <v>0.657</v>
       </c>
       <c r="R107" s="4" t="n">
-        <v>5.44</v>
+        <v>4.96</v>
       </c>
       <c r="S107" s="4" t="n">
         <v>20554</v>
@@ -8972,7 +8972,7 @@
         <v>0.49</v>
       </c>
       <c r="R108" t="n">
-        <v>4.88</v>
+        <v>4.34</v>
       </c>
       <c r="S108" t="n">
         <v>21408</v>
@@ -9052,7 +9052,7 @@
         <v>0.458</v>
       </c>
       <c r="R109" s="4" t="n">
-        <v>4.72</v>
+        <v>4.16</v>
       </c>
       <c r="S109" s="4" t="n">
         <v>19656</v>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -9578,12 +9578,6 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S116" t="n">
         <v>8028</v>
       </c>
@@ -9623,7 +9617,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G117" s="4" t="n">
@@ -9658,12 +9652,8 @@
       <c r="P117" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q117" s="4" t="n"/>
+      <c r="R117" s="4" t="n"/>
       <c r="S117" s="4" t="n">
         <v>5075</v>
       </c>
@@ -9703,7 +9693,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -9738,12 +9728,6 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S118" t="n">
         <v>5132</v>
       </c>
@@ -9783,7 +9767,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G119" s="4" t="n">
@@ -9818,12 +9802,8 @@
       <c r="P119" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q119" s="4" t="n"/>
+      <c r="R119" s="4" t="n"/>
       <c r="S119" s="4" t="n">
         <v>7784</v>
       </c>
@@ -9863,7 +9843,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -9898,12 +9878,6 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S120" t="n">
         <v>7633</v>
       </c>
@@ -9943,7 +9917,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G121" s="4" t="n">
@@ -9978,12 +9952,8 @@
       <c r="P121" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q121" s="4" t="n"/>
+      <c r="R121" s="4" t="n"/>
       <c r="S121" s="4" t="n">
         <v>7346</v>
       </c>
@@ -10062,7 +10032,7 @@
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S122" t="n">
         <v>11136</v>
@@ -10142,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="R123" s="4" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S123" s="4" t="n">
         <v>16248</v>
@@ -10222,7 +10192,7 @@
         <v>0.187</v>
       </c>
       <c r="R124" t="n">
-        <v>2.48</v>
+        <v>1.68</v>
       </c>
       <c r="S124" t="n">
         <v>16036</v>
@@ -10302,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="R125" s="4" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S125" s="4" t="n">
         <v>16222</v>
@@ -10382,7 +10352,7 @@
         <v>0.922</v>
       </c>
       <c r="R126" t="n">
-        <v>6.8</v>
+        <v>6.46</v>
       </c>
       <c r="S126" t="n">
         <v>35783</v>
@@ -10462,7 +10432,7 @@
         <v>1.058</v>
       </c>
       <c r="R127" s="4" t="n">
-        <v>7.36</v>
+        <v>7.08</v>
       </c>
       <c r="S127" s="4" t="n">
         <v>39686</v>
@@ -10992,7 +10962,7 @@
         <v>0.352</v>
       </c>
       <c r="R134" t="n">
-        <v>3.84</v>
+        <v>3.19</v>
       </c>
       <c r="S134" t="n">
         <v>12798</v>
@@ -11072,7 +11042,7 @@
         <v>0.338</v>
       </c>
       <c r="R135" s="4" t="n">
-        <v>3.52</v>
+        <v>2.83</v>
       </c>
       <c r="S135" s="4" t="n">
         <v>13319</v>
@@ -11152,7 +11122,7 @@
         <v>0.114</v>
       </c>
       <c r="R136" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="S136" t="n">
         <v>13107</v>
@@ -11232,7 +11202,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="R137" s="4" t="n">
-        <v>6.16</v>
+        <v>5.75</v>
       </c>
       <c r="S137" s="4" t="n">
         <v>32726</v>
@@ -11312,7 +11282,7 @@
         <v>1.4</v>
       </c>
       <c r="R138" t="n">
-        <v>8.48</v>
+        <v>8.32</v>
       </c>
       <c r="S138" t="n">
         <v>39648</v>
@@ -11392,7 +11362,7 @@
         <v>1.513</v>
       </c>
       <c r="R139" s="4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="S139" s="4" t="n">
         <v>40648</v>
@@ -12372,7 +12342,7 @@
         <v>0.194</v>
       </c>
       <c r="R152" t="n">
-        <v>2.56</v>
+        <v>1.77</v>
       </c>
       <c r="S152" t="n">
         <v>15438</v>
@@ -12452,7 +12422,7 @@
         <v>0.774</v>
       </c>
       <c r="R153" s="4" t="n">
-        <v>5.76</v>
+        <v>5.31</v>
       </c>
       <c r="S153" s="4" t="n">
         <v>31010</v>
@@ -12532,7 +12502,7 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="R154" t="n">
-        <v>6.08</v>
+        <v>5.66</v>
       </c>
       <c r="S154" t="n">
         <v>37095</v>
@@ -12612,7 +12582,7 @@
         <v>1.369</v>
       </c>
       <c r="R155" s="4" t="n">
-        <v>8.16</v>
+        <v>7.96</v>
       </c>
       <c r="S155" s="4" t="n">
         <v>23017</v>
@@ -12692,7 +12662,7 @@
         <v>1.389</v>
       </c>
       <c r="R156" t="n">
-        <v>8.32</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S156" t="n">
         <v>38871</v>
@@ -12772,7 +12742,7 @@
         <v>1.561</v>
       </c>
       <c r="R157" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S157" s="4" t="n">
         <v>49003</v>
@@ -15552,7 +15522,7 @@
         <v>0.209</v>
       </c>
       <c r="R194" t="n">
-        <v>2.64</v>
+        <v>1.86</v>
       </c>
       <c r="S194" t="n">
         <v>28664</v>
@@ -15632,7 +15602,7 @@
         <v>0.23</v>
       </c>
       <c r="R195" s="4" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="S195" s="4" t="n">
         <v>26138</v>
@@ -15712,7 +15682,7 @@
         <v>0.256</v>
       </c>
       <c r="R196" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="S196" t="n">
         <v>29261</v>
@@ -15792,7 +15762,7 @@
         <v>0.327</v>
       </c>
       <c r="R197" s="4" t="n">
-        <v>3.36</v>
+        <v>2.65</v>
       </c>
       <c r="S197" s="4" t="n">
         <v>27555</v>
@@ -15872,7 +15842,7 @@
         <v>0.297</v>
       </c>
       <c r="R198" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="S198" t="n">
         <v>30259</v>
@@ -15952,7 +15922,7 @@
         <v>0.26</v>
       </c>
       <c r="R199" s="4" t="n">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="S199" s="4" t="n">
         <v>34555</v>
@@ -17832,7 +17802,7 @@
         <v>0.785</v>
       </c>
       <c r="R224" t="n">
-        <v>5.92</v>
+        <v>5.49</v>
       </c>
       <c r="S224" t="n">
         <v>36299</v>
@@ -17912,7 +17882,7 @@
         <v>0.741</v>
       </c>
       <c r="R225" s="4" t="n">
-        <v>5.68</v>
+        <v>5.22</v>
       </c>
       <c r="S225" s="4" t="n">
         <v>39834</v>
@@ -17992,7 +17962,7 @@
         <v>1.765</v>
       </c>
       <c r="R226" t="n">
-        <v>9.279999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S226" t="n">
         <v>41072</v>
@@ -18072,7 +18042,7 @@
         <v>1.683</v>
       </c>
       <c r="R227" s="4" t="n">
-        <v>9.039999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="S227" s="4" t="n">
         <v>38909</v>
@@ -18152,7 +18122,7 @@
         <v>1.801</v>
       </c>
       <c r="R228" t="n">
-        <v>9.6</v>
+        <v>9.56</v>
       </c>
       <c r="S228" t="n">
         <v>34712</v>
@@ -18232,7 +18202,7 @@
         <v>2.481</v>
       </c>
       <c r="R229" s="4" t="n">
-        <v>9.92</v>
+        <v>9.91</v>
       </c>
       <c r="S229" s="4" t="n">
         <v>33863</v>
@@ -18312,7 +18282,7 @@
         <v>0.401</v>
       </c>
       <c r="R230" t="n">
-        <v>4.16</v>
+        <v>3.54</v>
       </c>
       <c r="S230" t="n">
         <v>18691</v>
@@ -18392,7 +18362,7 @@
         <v>0.371</v>
       </c>
       <c r="R231" s="4" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="S231" s="4" t="n">
         <v>20223</v>
@@ -18472,7 +18442,7 @@
         <v>0.888</v>
       </c>
       <c r="R232" t="n">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="S232" t="n">
         <v>23658</v>
@@ -18552,7 +18522,7 @@
         <v>0.912</v>
       </c>
       <c r="R233" s="4" t="n">
-        <v>6.64</v>
+        <v>6.28</v>
       </c>
       <c r="S233" s="4" t="n">
         <v>26315</v>
@@ -18632,7 +18602,7 @@
         <v>2.144</v>
       </c>
       <c r="R234" t="n">
-        <v>9.76</v>
+        <v>9.73</v>
       </c>
       <c r="S234" t="n">
         <v>27291</v>
@@ -18712,7 +18682,7 @@
         <v>2.002</v>
       </c>
       <c r="R235" s="4" t="n">
-        <v>9.68</v>
+        <v>9.65</v>
       </c>
       <c r="S235" s="4" t="n">
         <v>32962</v>
@@ -19242,7 +19212,7 @@
         <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S242" t="n">
         <v>10132</v>
@@ -19322,7 +19292,7 @@
         <v>0</v>
       </c>
       <c r="R243" s="4" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S243" s="4" t="n">
         <v>9675</v>
@@ -19402,7 +19372,7 @@
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S244" t="n">
         <v>13097</v>
@@ -19482,7 +19452,7 @@
         <v>0</v>
       </c>
       <c r="R245" s="4" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S245" s="4" t="n">
         <v>10884</v>
@@ -19562,7 +19532,7 @@
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S246" t="n">
         <v>9229</v>
@@ -19642,7 +19612,7 @@
         <v>0.108</v>
       </c>
       <c r="R247" s="4" t="n">
-        <v>1.84</v>
+        <v>0.97</v>
       </c>
       <c r="S247" s="4" t="n">
         <v>9248</v>
@@ -21522,7 +21492,7 @@
         <v>0.916</v>
       </c>
       <c r="R272" t="n">
-        <v>6.72</v>
+        <v>6.37</v>
       </c>
       <c r="S272" t="n">
         <v>37659</v>
@@ -21602,7 +21572,7 @@
         <v>1.235</v>
       </c>
       <c r="R273" s="4" t="n">
-        <v>7.76</v>
+        <v>7.52</v>
       </c>
       <c r="S273" s="4" t="n">
         <v>36429</v>
@@ -21682,7 +21652,7 @@
         <v>1.143</v>
       </c>
       <c r="R274" t="n">
-        <v>7.6</v>
+        <v>7.35</v>
       </c>
       <c r="S274" t="n">
         <v>41986</v>
@@ -21762,7 +21732,7 @@
         <v>1.252</v>
       </c>
       <c r="R275" s="4" t="n">
-        <v>7.84</v>
+        <v>7.61</v>
       </c>
       <c r="S275" s="4" t="n">
         <v>41936</v>
@@ -21842,7 +21812,7 @@
         <v>1.2</v>
       </c>
       <c r="R276" t="n">
-        <v>7.68</v>
+        <v>7.43</v>
       </c>
       <c r="S276" t="n">
         <v>45016</v>
@@ -21922,7 +21892,7 @@
         <v>0.959</v>
       </c>
       <c r="R277" s="4" t="n">
-        <v>7.12</v>
+        <v>6.81</v>
       </c>
       <c r="S277" s="4" t="n">
         <v>42226</v>
@@ -22456,7 +22426,7 @@
         <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S284" t="n">
         <v>20599</v>
@@ -22536,7 +22506,7 @@
         <v>0.449</v>
       </c>
       <c r="R285" s="4" t="n">
-        <v>4.64</v>
+        <v>4.07</v>
       </c>
       <c r="S285" s="4" t="n">
         <v>23401</v>
@@ -22616,7 +22586,7 @@
         <v>0.569</v>
       </c>
       <c r="R286" t="n">
-        <v>5.28</v>
+        <v>4.78</v>
       </c>
       <c r="S286" t="n">
         <v>26383</v>
@@ -22696,7 +22666,7 @@
         <v>0.888</v>
       </c>
       <c r="R287" s="4" t="n">
-        <v>6.48</v>
+        <v>6.11</v>
       </c>
       <c r="S287" s="4" t="n">
         <v>27038</v>
@@ -22776,7 +22746,7 @@
         <v>1.08</v>
       </c>
       <c r="R288" t="n">
-        <v>7.52</v>
+        <v>7.26</v>
       </c>
       <c r="S288" t="n">
         <v>29155</v>
@@ -22856,7 +22826,7 @@
         <v>1.79</v>
       </c>
       <c r="R289" s="4" t="n">
-        <v>9.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S289" s="4" t="n">
         <v>32673</v>
@@ -26047,7 +26017,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -26082,12 +26052,6 @@
       <c r="P332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
-      <c r="R332" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S332" t="n">
         <v>2088</v>
       </c>
@@ -26127,7 +26091,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G333" s="4" t="n">
@@ -26162,12 +26126,8 @@
       <c r="P333" s="4" t="n">
         <v>0.181</v>
       </c>
-      <c r="Q333" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R333" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q333" s="4" t="n"/>
+      <c r="R333" s="4" t="n"/>
       <c r="S333" s="4" t="n">
         <v>5519</v>
       </c>
@@ -26207,7 +26167,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -26242,12 +26202,6 @@
       <c r="P334" t="n">
         <v>0.743</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
-      <c r="R334" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S334" t="n">
         <v>5385</v>
       </c>
@@ -26287,7 +26241,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G335" s="4" t="n">
@@ -26322,12 +26276,8 @@
       <c r="P335" s="4" t="n">
         <v>1.322</v>
       </c>
-      <c r="Q335" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R335" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q335" s="4" t="n"/>
+      <c r="R335" s="4" t="n"/>
       <c r="S335" s="4" t="n">
         <v>3781</v>
       </c>
@@ -26367,7 +26317,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -26402,12 +26352,6 @@
       <c r="P336" t="n">
         <v>0.869</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
-      <c r="R336" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S336" t="n">
         <v>3452</v>
       </c>
@@ -26447,7 +26391,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G337" s="4" t="n">
@@ -26482,12 +26426,8 @@
       <c r="P337" s="4" t="n">
         <v>0.862</v>
       </c>
-      <c r="Q337" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R337" s="4" t="n">
-        <v>0.84</v>
-      </c>
+      <c r="Q337" s="4" t="n"/>
+      <c r="R337" s="4" t="n"/>
       <c r="S337" s="4" t="n">
         <v>8118</v>
       </c>
@@ -27466,7 +27406,7 @@
         <v>0</v>
       </c>
       <c r="R350" t="n">
-        <v>0.84</v>
+        <v>0.4</v>
       </c>
       <c r="S350" t="n">
         <v>20759</v>
@@ -27546,7 +27486,7 @@
         <v>0.259</v>
       </c>
       <c r="R351" s="4" t="n">
-        <v>2.96</v>
+        <v>2.21</v>
       </c>
       <c r="S351" s="4" t="n">
         <v>23151</v>
@@ -27626,7 +27566,7 @@
         <v>0.44</v>
       </c>
       <c r="R352" t="n">
-        <v>4.56</v>
+        <v>3.98</v>
       </c>
       <c r="S352" t="n">
         <v>27286</v>
@@ -27706,7 +27646,7 @@
         <v>1.053</v>
       </c>
       <c r="R353" s="4" t="n">
-        <v>7.28</v>
+        <v>6.99</v>
       </c>
       <c r="S353" s="4" t="n">
         <v>22793</v>
@@ -27786,7 +27726,7 @@
         <v>0.879</v>
       </c>
       <c r="R354" t="n">
-        <v>6.32</v>
+        <v>5.93</v>
       </c>
       <c r="S354" t="n">
         <v>22176</v>
@@ -27866,7 +27806,7 @@
         <v>0.719</v>
       </c>
       <c r="R355" s="4" t="n">
-        <v>5.6</v>
+        <v>5.13</v>
       </c>
       <c r="S355" s="4" t="n">
         <v>25041</v>
@@ -28396,7 +28336,7 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="R362" t="n">
-        <v>6.96</v>
+        <v>6.64</v>
       </c>
       <c r="S362" t="n">
         <v>20318</v>
@@ -28476,7 +28416,7 @@
         <v>1.465</v>
       </c>
       <c r="R363" s="4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="S363" s="4" t="n">
         <v>21847</v>
@@ -28556,7 +28496,7 @@
         <v>1.708</v>
       </c>
       <c r="R364" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S364" t="n">
         <v>19617</v>
@@ -28636,7 +28576,7 @@
         <v>1.065</v>
       </c>
       <c r="R365" s="4" t="n">
-        <v>7.44</v>
+        <v>7.17</v>
       </c>
       <c r="S365" s="4" t="n">
         <v>22070</v>
@@ -28716,7 +28656,7 @@
         <v>2.394</v>
       </c>
       <c r="R366" t="n">
-        <v>9.84</v>
+        <v>9.82</v>
       </c>
       <c r="S366" t="n">
         <v>20467</v>
@@ -28876,7 +28816,7 @@
         <v>0.155</v>
       </c>
       <c r="R368" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="S368" t="n">
         <v>29075</v>
@@ -28956,7 +28896,7 @@
         <v>0.437</v>
       </c>
       <c r="R369" s="4" t="n">
-        <v>4.48</v>
+        <v>3.89</v>
       </c>
       <c r="S369" s="4" t="n">
         <v>30918</v>
@@ -29036,7 +28976,7 @@
         <v>0.406</v>
       </c>
       <c r="R370" t="n">
-        <v>4.24</v>
+        <v>3.63</v>
       </c>
       <c r="S370" t="n">
         <v>29529</v>
@@ -29116,7 +29056,7 @@
         <v>0.436</v>
       </c>
       <c r="R371" s="4" t="n">
-        <v>4.4</v>
+        <v>3.81</v>
       </c>
       <c r="S371" s="4" t="n">
         <v>30991</v>
@@ -29196,7 +29136,7 @@
         <v>0.697</v>
       </c>
       <c r="R372" t="n">
-        <v>5.52</v>
+        <v>5.04</v>
       </c>
       <c r="S372" t="n">
         <v>27967</v>
@@ -29276,7 +29216,7 @@
         <v>0.881</v>
       </c>
       <c r="R373" s="4" t="n">
-        <v>6.4</v>
+        <v>6.02</v>
       </c>
       <c r="S373" s="4" t="n">
         <v>28957</v>
@@ -33309,7 +33249,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -34009,7 +33949,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="n">

--- a/docs/exports/verity_esg_scores.xlsx
+++ b/docs/exports/verity_esg_scores.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scores by year'!$A$1:$Y$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Company averages'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Company averages'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -516,98 +516,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Terms material to a company's SASB industry are weighted 1.5; others 1.0.</t>
+          <t>Term concepts: E=24, S=22 (27 phrases), G=34 (36 phrases), General=8, Banking add-on=9.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scores are rank-normalised 0–100 across all 390 reports; 100 = most disclosure.</t>
+          <t>Terms material to a company's SASB industry are weighted 1.5; others 1.0.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Scores are rank-normalised 0-100 across all 390 reports; 100 = most disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Composite = average of Environmental, Social, Governance, and General scores.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>How to read a 0–100 score</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100 = the report with the most disclosure in this sample for that pillar.</t>
+          <t>How to read a 0–100 score</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0   = the report with the least.</t>
+          <t>100 = the report with the most disclosure in this sample for that pillar.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>0   = the report with the least.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Scores show relative position within this sample, not absolute quality.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Methodology page: see the Verity web dashboard → Methodology.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scores by year   — one row per company-year</t>
+          <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Company averages — six-year averages, ranked 1–65</t>
+          <t>Scores by year   — one row per company-year</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Robustness       — main composite vs four variants + correlations</t>
+          <t>Company averages — six-year averages, ranked 1–65</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>Robustness       — main composite vs seven variants + correlations</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Column guide     — definition and unit of every column</t>
         </is>
@@ -34211,7 +34218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34224,8 +34231,9 @@
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34281,10 +34289,15 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Avg General (0-100)</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>Avg Composite (0-100)</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Years scored</t>
         </is>
@@ -34334,9 +34347,12 @@
         <v>55.38</v>
       </c>
       <c r="K2" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="L2" t="n">
         <v>74.92</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34384,9 +34400,12 @@
         <v>68.77</v>
       </c>
       <c r="K3" s="4" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="L3" s="4" t="n">
         <v>72.08</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34434,9 +34453,12 @@
         <v>75.65000000000001</v>
       </c>
       <c r="K4" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L4" t="n">
         <v>69.15000000000001</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34484,9 +34506,12 @@
         <v>76.37</v>
       </c>
       <c r="K5" s="4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>68.45</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34534,9 +34559,12 @@
         <v>20.18</v>
       </c>
       <c r="K6" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="L6" t="n">
         <v>68.45</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34584,9 +34612,12 @@
         <v>60.47</v>
       </c>
       <c r="K7" s="4" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="L7" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34634,9 +34665,12 @@
         <v>56.28</v>
       </c>
       <c r="K8" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="L8" t="n">
         <v>64.81999999999999</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34684,9 +34718,12 @@
         <v>87.34999999999999</v>
       </c>
       <c r="K9" s="4" t="n">
+        <v>72.92</v>
+      </c>
+      <c r="L9" s="4" t="n">
         <v>64.06999999999999</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34734,9 +34771,12 @@
         <v>62.08</v>
       </c>
       <c r="K10" t="n">
+        <v>81.38</v>
+      </c>
+      <c r="L10" t="n">
         <v>63.85</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34784,9 +34824,12 @@
         <v>23.97</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>70.62</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>63.42</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34834,9 +34877,12 @@
         <v>16.03</v>
       </c>
       <c r="K12" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="L12" t="n">
         <v>61.22</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34884,9 +34930,12 @@
         <v>22.4</v>
       </c>
       <c r="K13" s="4" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="L13" s="4" t="n">
         <v>60.85</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34934,9 +34983,12 @@
         <v>94.53</v>
       </c>
       <c r="K14" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="L14" t="n">
         <v>60.3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -34984,9 +35036,12 @@
         <v>78.37</v>
       </c>
       <c r="K15" s="4" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="L15" s="4" t="n">
         <v>60.15</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35034,9 +35089,12 @@
         <v>33.08</v>
       </c>
       <c r="K16" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="L16" t="n">
         <v>60.13</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35084,9 +35142,12 @@
         <v>33.17</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L17" s="4" t="n">
         <v>59.07</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35134,9 +35195,12 @@
         <v>49.65</v>
       </c>
       <c r="K18" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="L18" t="n">
         <v>58.73</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35184,9 +35248,12 @@
         <v>90.81999999999999</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>24.03</v>
+      </c>
+      <c r="L19" s="4" t="n">
         <v>58.72</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35234,9 +35301,12 @@
         <v>86.09999999999999</v>
       </c>
       <c r="K20" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="L20" t="n">
         <v>58.58</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35284,9 +35354,12 @@
         <v>44.48</v>
       </c>
       <c r="K21" s="4" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="L21" s="4" t="n">
         <v>58.12</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35334,9 +35407,12 @@
         <v>75.02</v>
       </c>
       <c r="K22" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="L22" t="n">
         <v>57.85</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35384,9 +35460,12 @@
         <v>45.3</v>
       </c>
       <c r="K23" s="4" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="L23" s="4" t="n">
         <v>57.83</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35434,9 +35513,12 @@
         <v>40.02</v>
       </c>
       <c r="K24" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="L24" t="n">
         <v>57.78</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35484,9 +35566,12 @@
         <v>29.42</v>
       </c>
       <c r="K25" s="4" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="L25" s="4" t="n">
         <v>57.1</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35534,9 +35619,12 @@
         <v>60.47</v>
       </c>
       <c r="K26" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="L26" t="n">
         <v>56.4</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35584,9 +35672,12 @@
         <v>50.8</v>
       </c>
       <c r="K27" s="4" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="L27" s="4" t="n">
         <v>55.82</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="M27" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35634,9 +35725,12 @@
         <v>19.38</v>
       </c>
       <c r="K28" t="n">
+        <v>78.15000000000001</v>
+      </c>
+      <c r="L28" t="n">
         <v>55.32</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35684,9 +35778,12 @@
         <v>40.25</v>
       </c>
       <c r="K29" s="4" t="n">
+        <v>77.05</v>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>55.2</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35734,9 +35831,12 @@
         <v>53.87</v>
       </c>
       <c r="K30" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="L30" t="n">
         <v>55.17</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35784,9 +35884,12 @@
         <v>69.18000000000001</v>
       </c>
       <c r="K31" s="4" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="L31" s="4" t="n">
         <v>54.93</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35834,9 +35937,12 @@
         <v>80.65000000000001</v>
       </c>
       <c r="K32" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="L32" t="n">
         <v>54.73</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35884,9 +35990,12 @@
         <v>22.75</v>
       </c>
       <c r="K33" s="4" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="L33" s="4" t="n">
         <v>53.38</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35934,9 +36043,12 @@
         <v>53.37</v>
       </c>
       <c r="K34" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="L34" t="n">
         <v>52.33</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -35984,9 +36096,12 @@
         <v>53.05</v>
       </c>
       <c r="K35" s="4" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="L35" s="4" t="n">
         <v>51.9</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36034,9 +36149,12 @@
         <v>73.81999999999999</v>
       </c>
       <c r="K36" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="L36" t="n">
         <v>50.98</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36084,9 +36202,12 @@
         <v>10.72</v>
       </c>
       <c r="K37" s="4" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="L37" s="4" t="n">
         <v>50.52</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36134,9 +36255,12 @@
         <v>59.72</v>
       </c>
       <c r="K38" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="L38" t="n">
         <v>50.33</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36184,9 +36308,12 @@
         <v>32.15</v>
       </c>
       <c r="K39" s="4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="L39" s="4" t="n">
         <v>48.95</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36234,9 +36361,12 @@
         <v>41.03</v>
       </c>
       <c r="K40" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="L40" t="n">
         <v>48.57</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36284,9 +36414,12 @@
         <v>13.07</v>
       </c>
       <c r="K41" s="4" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="L41" s="4" t="n">
         <v>47.72</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36334,9 +36467,12 @@
         <v>24.85</v>
       </c>
       <c r="K42" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="L42" t="n">
         <v>47.67</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36384,9 +36520,12 @@
         <v>73.25</v>
       </c>
       <c r="K43" s="4" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="L43" s="4" t="n">
         <v>47.57</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="M43" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36434,9 +36573,12 @@
         <v>70.48</v>
       </c>
       <c r="K44" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="L44" t="n">
         <v>47.53</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36484,9 +36626,12 @@
         <v>78.18000000000001</v>
       </c>
       <c r="K45" s="4" t="n">
+        <v>39.92</v>
+      </c>
+      <c r="L45" s="4" t="n">
         <v>45.72</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36534,9 +36679,12 @@
         <v>37.82</v>
       </c>
       <c r="K46" t="n">
+        <v>65.33</v>
+      </c>
+      <c r="L46" t="n">
         <v>45.4</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36584,9 +36732,12 @@
         <v>58.97</v>
       </c>
       <c r="K47" s="4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L47" s="4" t="n">
         <v>44.17</v>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="M47" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36634,9 +36785,12 @@
         <v>28.72</v>
       </c>
       <c r="K48" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="L48" t="n">
         <v>42.85</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36684,9 +36838,12 @@
         <v>26.23</v>
       </c>
       <c r="K49" s="4" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L49" s="4" t="n">
         <v>41.45</v>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36734,9 +36891,12 @@
         <v>29.95</v>
       </c>
       <c r="K50" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="L50" t="n">
         <v>41.37</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36784,9 +36944,12 @@
         <v>75.77</v>
       </c>
       <c r="K51" s="4" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="L51" s="4" t="n">
         <v>41.25</v>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36834,9 +36997,12 @@
         <v>54.23</v>
       </c>
       <c r="K52" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="L52" t="n">
         <v>39.92</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36884,9 +37050,12 @@
         <v>95.77</v>
       </c>
       <c r="K53" s="4" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="L53" s="4" t="n">
         <v>39.82</v>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36934,9 +37103,12 @@
         <v>59.42</v>
       </c>
       <c r="K54" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="L54" t="n">
         <v>38.27</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>6</v>
       </c>
     </row>
@@ -36984,9 +37156,12 @@
         <v>31.15</v>
       </c>
       <c r="K55" s="4" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="L55" s="4" t="n">
         <v>35.82</v>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37034,9 +37209,12 @@
         <v>23.82</v>
       </c>
       <c r="K56" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="L56" t="n">
         <v>35.08</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37084,9 +37262,12 @@
         <v>48.75</v>
       </c>
       <c r="K57" s="4" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="L57" s="4" t="n">
         <v>34.02</v>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37134,9 +37315,12 @@
         <v>23.87</v>
       </c>
       <c r="K58" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="L58" t="n">
         <v>32.17</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37184,9 +37368,12 @@
         <v>99.34999999999999</v>
       </c>
       <c r="K59" s="4" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="L59" s="4" t="n">
         <v>31.67</v>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37234,9 +37421,12 @@
         <v>14.25</v>
       </c>
       <c r="K60" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="L60" t="n">
         <v>29.92</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37284,9 +37474,12 @@
         <v>26.63</v>
       </c>
       <c r="K61" s="4" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="L61" s="4" t="n">
         <v>29.78</v>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37334,9 +37527,12 @@
         <v>37.18</v>
       </c>
       <c r="K62" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="L62" t="n">
         <v>27.4</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37384,9 +37580,12 @@
         <v>52.78</v>
       </c>
       <c r="K63" s="4" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="L63" s="4" t="n">
         <v>27.25</v>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37434,9 +37633,12 @@
         <v>78.78</v>
       </c>
       <c r="K64" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="L64" t="n">
         <v>26.6</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37484,9 +37686,12 @@
         <v>13.03</v>
       </c>
       <c r="K65" s="4" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L65" s="4" t="n">
         <v>21.2</v>
       </c>
-      <c r="L65" s="4" t="n">
+      <c r="M65" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -37534,14 +37739,17 @@
         <v>27.62</v>
       </c>
       <c r="K66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L66" t="n">
         <v>11.08</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <conditionalFormatting sqref="H2:H66">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -37590,6 +37798,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L66">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
